--- a/docs/PRAP_UI_Component_List_v2.0.xlsx
+++ b/docs/PRAP_UI_Component_List_v2.0.xlsx
@@ -1137,7 +1137,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>68 components. 27 Keep, 13 Change (amber), 6 added by those changes (green). Your comments are quoted exactly as written.</t>
+          <t>68 components. 27 Keep, 13 Change (amber), 5 added by those changes (green). Your comments are quoted exactly as written.</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>NOT IMPLEMENTED. [FIXED v2.0] v1.0 recorded this as 'Keep - unchanged', which read as built. It never was: there is no virtualisation anywhere in src/. Both Overall tables render every row. At the sizes in use that is fast enough, and the chart caps (LIMIT 20 bands, 12 lines) keep the drawing bounded - but REQ-DSH-09 and REQ-NFR-03 name a thousand people, and at that size this is an open performance risk rather than a solved problem. Listed here so it is not mistaken for done.</t>
+          <t>NOT IMPLEMENTED, AND NOW MEASURED. [FIXED v2.0] v1.0 recorded this as 'Keep - unchanged', which read as built. It never was: there is no virtualisation anywhere in src/, and both Overall tables render every row. MEASURED at exactly the volume REQ-NFR-03 names - 100 projects, 1,000 people, 8,000 assignments, a 60-month horizon (tools/build_stress_workbook.py and tools/measure_scale.py): the Overall tab takes 3,058 ms to switch to, worst case 4,537 ms, drawing 67,222 cells in 1,102 rows. Budget was 1,000 ms, set before the numbers were seen. THREE TIMES OVER, so this is a real defect rather than a theoretical one, and it is exactly the two tables this component names. FOR SCALE, the same measurement at the sizes in use: 10x10 switches in 156 ms and 50x50 in 374 ms, both comfortable. The problem appears between 50 and 1,000 people, not before. WHAT VIRTUALISATION WOULD NOT FIX. The import at that volume is 7,328 ms against a 5,000 ms budget, and 3,076 ms of that is the CALCULATION alone - 180,160 person-months. Virtualisation touches neither the calculation nor the workbook parse, so it answers the tab and about half of the import. Editing (98 ms) and filtering (49 ms) are already inside budget at full volume and would not change.</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -2802,34 +2802,34 @@
       <c r="I43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="14" t="inlineStr">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>A-01</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>Assumptions tab</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>Standard period weights</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
-        <is>
-          <t>PeriodWeightStandard as a matrix - phase down the side, period across, shaded by magnitude.</t>
-        </is>
-      </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>[FIXED v2.0] Standard period FTE for project types</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>PeriodFTEStandard as a matrix - type and phase down the side, period across, shaded by magnitude. [FIXED v2.0] v1.0 called this 'Standard period weights' and named the sheet PeriodWeightStandard. Both were renamed at R-33: the column holds a monthly FTE, a MAGNITUDE, and calling it a weight is most of why it went unused - a weight reads like something to multiply by. Caught by the new component check in check_consistency.py, not by reading.</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>REQ-DSH-11</t>
         </is>
       </c>
-      <c r="F44" s="14" t="inlineStr"/>
-      <c r="G44" s="15" t="inlineStr"/>
-      <c r="H44" s="15" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr"/>
+      <c r="G44" s="13" t="inlineStr"/>
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t>Added for G-07. Shown as a matrix, not 48 flat rows: it is a standard, and a standard is read across. 'Others' projects are absent by design - their weights are hand-entered per project.</t>
         </is>
@@ -3083,12 +3083,12 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>[NEW v2.0] Monthly resource trend (line chart)</t>
+          <t>[NEW v2.0] Monthly resource trend / Monthly load trend (line chart)</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>One line per project on a shared baseline, capped at the 12 largest by total. A stack answers 'what is this month made of'; only lines answer 'is this one rising or falling', because in a stack every band's baseline moves with the bands beneath it. Hover gives the line's total, mean and peak month.</t>
+          <t>One line per project on a shared baseline, capped at the 12 largest by total. The person tab carries the same component under the title 'Monthly load trend', one line per person with the over-allocation ceiling drawn. A stack answers 'what is this month made of'; only lines answer 'is this one rising or falling', because in a stack every band's baseline moves with the bands beneath it. Hover gives the line's total, mean and peak month.</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -3962,7 +3962,7 @@
         <v>9</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">

--- a/docs/PRAP_UI_Component_List_v2.0.xlsx
+++ b/docs/PRAP_UI_Component_List_v2.0.xlsx
@@ -2780,7 +2780,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>NOT IMPLEMENTED, AND NOW MEASURED. [FIXED v2.0] v1.0 recorded this as 'Keep - unchanged', which read as built. It never was: there is no virtualisation anywhere in src/, and both Overall tables render every row. MEASURED at exactly the volume REQ-NFR-03 names - 100 projects, 1,000 people, 8,000 assignments, a 60-month horizon (tools/build_stress_workbook.py and tools/measure_scale.py): the Overall tab takes 3,058 ms to switch to, worst case 4,537 ms, drawing 67,222 cells in 1,102 rows. Budget was 1,000 ms, set before the numbers were seen. THREE TIMES OVER, so this is a real defect rather than a theoretical one, and it is exactly the two tables this component names. FOR SCALE, the same measurement at the sizes in use: 10x10 switches in 156 ms and 50x50 in 374 ms, both comfortable. The problem appears between 50 and 1,000 people, not before. WHAT VIRTUALISATION WOULD NOT FIX. The import at that volume is 7,328 ms against a 5,000 ms budget, and 3,076 ms of that is the CALCULATION alone - 180,160 person-months. Virtualisation touches neither the calculation nor the workbook parse, so it answers the tab and about half of the import. Editing (98 ms) and filtering (49 ms) are already inside budget at full volume and would not change.</t>
+          <t>NOT IMPLEMENTED, AND NOW MEASURED. [FIXED v2.0] v1.0 recorded this as 'Keep - unchanged', which read as built. It never was: there is no virtualisation anywhere in src/, and both Overall tables render every row. MEASURED at exactly the volume REQ-NFR-03 names - 100 projects, 1,000 people, 8,000 assignments, a 60-month horizon (tools/build_stress_workbook.py and tools/measure_scale.py): the Overall tab takes 3,058 ms to switch to, worst case 4,537 ms, drawing 67,222 cells in 1,102 rows. Budget was 1,000 ms, set before the numbers were seen. THREE TIMES OVER, so this is a real defect rather than a theoretical one, and it is exactly the two tables this component names. AND AT THE SCALE ACTUALLY IN USE IT IS NOT A DEFECT AT ALL. Measured across the range (50 projects throughout, 60-month horizon), the Overall tab takes: 50 people 369 ms, 100 people 503 ms, 200 people 786 ms, 400 people 1,044 ms, 1,000 people 3,207 ms. THE BUDGET IS CROSSED AT ABOUT 400 PEOPLE. At 50 projects x 100 people - the volume put forward as the real operating requirement - the tightest measurement of any kind sits at 55% of its budget, which is roughly a factor of two of headroom. Whether this component needs building therefore depends entirely on which volume the requirement names, and that is a decision about the requirement rather than about the code. WHAT VIRTUALISATION WOULD NOT FIX. The import at that volume is 7,328 ms against a 5,000 ms budget, and 3,076 ms of that is the CALCULATION alone - 180,160 person-months. Virtualisation touches neither the calculation nor the workbook parse, so it answers the tab and about half of the import. Editing (98 ms) and filtering (49 ms) are already inside budget at full volume and would not change.</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
